--- a/artfynd/A 7799-2024 artfynd.xlsx
+++ b/artfynd/A 7799-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,11 +1374,11 @@
         <v>115749503</v>
       </c>
       <c r="B8" t="n">
-        <v>57271</v>
+        <v>57363</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1615,14 +1615,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115768721</v>
+        <v>115768846</v>
       </c>
       <c r="B10" t="n">
-        <v>57271</v>
+        <v>57363</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789575</v>
+        <v>789629</v>
       </c>
       <c r="R10" t="n">
-        <v>7285944</v>
+        <v>7285910</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Träd med tydliga hackspår och hål av mindre hackspetten</t>
+          <t>Flera små hackade hål i en gammal björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,139 +1745,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>115768846</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Hildingsro, Alterdal NO Sikfors, Nb</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>789629</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7285910</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Norrfjärden</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera små hackade hål i en gammal björk</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Boreal blandskog, kontinuitetsskog?, många gamla träd (tall, gran, björk, al, pil osv), liggande och stående döda träd, hög biodiversitet</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Corina Delling</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Corina Delling</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
